--- a/data_folder/bev_electronics_metals/input_data/case.xlsx
+++ b/data_folder/bev_electronics_metals/input_data/case.xlsx
@@ -665,7 +665,6 @@
           <t>component</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -920,12 +919,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -952,12 +951,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -979,7 +978,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -989,7 +988,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hulk_transfer</t>
+          <t>stays_in_car</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,17 +1010,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_cu_own</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1043,17 +1042,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_alalloy_own</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1075,17 +1074,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_fealloy_own</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1107,17 +1106,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F_loss_separation</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1144,17 +1143,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_cu_general</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1176,17 +1175,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_alalloy_general</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1208,17 +1207,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_fealloy_general</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1240,17 +1239,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_loss_general</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>shredding</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hammer_mill</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1283,22 +1282,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1386,7 +1385,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1406,7 +1405,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1417,7 +1416,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1427,7 +1426,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a traction or auxiliary motor is a discrete, heavy, valuable part and a dismantler goes for it.</t>
+          <t>PLACEHOLDER (Claude, not data) -- a motor is a heavy, valuable, discrete part and a worker goes for it.</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1448,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1459,28 +1458,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1490,14 +1485,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- harness removal is slow manual work and most of it stays in the car.</t>
+          <t>COMPUTED, not typed: whatever was not taken out is still in the car. Nothing is lost by not being disassembled.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1512,7 +1507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1527,33 +1522,25 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.1125</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.3625</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>stays_in_car</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what is dismantled, widened. There is no loss here -- dismantling SORTS material, it does not destroy it -- so this is what stays in the car, and it goes to the shredder.</t>
+          <t>DEFINITIONAL: the car goes to the shredder, so what is in it goes too. Not a measurement and not uncertain.</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1562,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1590,23 +1577,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>dismantling</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1616,14 +1603,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what is dismantled, widened. There is no loss here -- dismantling SORTS material, it does not destroy it -- so this is what stays in the car, and it goes to the shredder.</t>
+          <t>PLACEHOLDER (Claude, not data) -- pulling a harness out is slow manual work, so most of it stays in the car.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_collected</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1638,7 +1625,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F_shredded</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1648,37 +1635,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>hulk_transfer</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>definitional</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>DEFINITIONAL -- a component that was not dismantled is still in the car, and the car goes to the shredder. Not a coefficient and not uncertain.</t>
+          <t>COMPUTED, not typed: whatever was not taken out is still in the car. Nothing is lost by not being disassembled.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_in_car</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1708,7 +1699,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1716,7 +1707,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>hulk_transfer</t>
+          <t>stays_in_car</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1726,14 +1717,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>DEFINITIONAL -- a component that was not dismantled is still in the car, and the car goes to the shredder. Not a coefficient and not uncertain.</t>
+          <t>DEFINITIONAL: the car goes to the shredder, so what is in it goes too. Not a measurement and not uncertain.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1748,7 +1739,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_cu_own</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1758,20 +1749,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>alalloy</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1781,14 +1780,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- alalloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1803,7 +1802,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1818,23 +1817,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1844,14 +1839,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a harness or a winding handled on its own line granulates and separates cleanly. In a hulk the wire disperses and much of it reports to the ASR or contaminates the ferrous fraction.</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1866,7 +1861,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_alalloy_own</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1876,20 +1871,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fealloy</t>
+          <t>alalloy</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1899,14 +1902,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- fealloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1921,7 +1924,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1931,28 +1934,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>alalloy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1962,14 +1961,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1979,12 +1978,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_fealloy_own</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1994,7 +1993,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>fealloy</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2009,13 +2008,13 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2025,14 +2024,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- a harness or a winding handled on its own line granulates and separates cleanly. In a hulk the wire disperses and much of it reports to the ASR or contaminates the ferrous fraction.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2047,7 +2046,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2057,28 +2056,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>alalloy</t>
+          <t>fealloy</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2088,14 +2083,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- eddy-current separation is reliable. What comes out is the ALLOY: the silicon, magnesium and copper alloyed into it stay in it and are not recovered separately.</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2110,7 +2105,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2120,12 +2115,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2133,7 +2128,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2143,14 +2138,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2160,12 +2155,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_cu_own</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2175,20 +2170,28 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>fealloy</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2198,14 +2201,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- fealloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2215,12 +2218,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_loss_own</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2230,28 +2233,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2261,14 +2260,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,12 +2277,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_cu_general</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2298,32 +2297,40 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for copper.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2338,7 +2345,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_loss_general</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2348,37 +2355,41 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>alalloy</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- alalloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2393,7 +2404,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_alalloy_general</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2403,37 +2414,45 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>alalloy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for aluminium alloy.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2448,7 +2467,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_loss_general</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2458,45 +2477,41 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>fealloy</t>
+          <t>alalloy</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- magnetic separation is the most dependable step in either route, which is why the shredded figure is barely below the dedicated one. The stream is steel, cast iron AND the ferrite magnets -- ferrite is ferrimagnetic and leaves with the ferrous fraction as an impurity in the steel.</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2511,7 +2526,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_fealloy_general</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2521,45 +2536,45 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>fealloy</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>decision: unspecified material is not recovered</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for steel alloy.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2569,12 +2584,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wiring</t>
+          <t>Motors</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_loss_general</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2584,37 +2599,41 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>fealloy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2629,7 +2648,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F_loss_separation</t>
+          <t>F_loss_general</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2639,45 +2658,37 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>alalloy</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2687,12 +2698,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F_loss_separation</t>
+          <t>F_cu_general</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2707,40 +2718,40 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0375</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.2875</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
+          <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for copper.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_shredded</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2750,12 +2761,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Motors</t>
+          <t>Wiring</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>F_loss_separation</t>
+          <t>F_loss_general</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2765,1387 +2776,38 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fealloy</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.0375</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.2875</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>dedicated</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>F_dismantled</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>F_loss_separation</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>separation</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>decision: unspecified material is not recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>F_dismantled</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>F_loss_separation</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.0375</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.2875</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>separation</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>F_recovered_cu</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>alalloy</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- alalloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>F_recovered_cu</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- a harness or a winding handled on its own line granulates and separates cleanly. In a hulk the wire disperses and much of it reports to the ASR or contaminates the ferrous fraction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>F_recovered_cu</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>fealloy</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- fealloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>F_recovered_cu</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>decision: unspecified material is not recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>F_recovered_cu</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- a harness or a winding handled on its own line granulates and separates cleanly. In a hulk the wire disperses and much of it reports to the ASR or contaminates the ferrous fraction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>F_recovered_al_alloy</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>alalloy</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- eddy-current separation is reliable. What comes out is the ALLOY: the silicon, magnesium and copper alloyed into it stay in it and are not recovered separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>F_recovered_al_alloy</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>F_recovered_al_alloy</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>fealloy</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- fealloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>F_recovered_al_alloy</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>decision: unspecified material is not recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>F_recovered_al_alloy</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>F_recovered_fe_alloy</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>alalloy</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- alalloy does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>F_recovered_fe_alloy</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>F_recovered_fe_alloy</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>fealloy</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- magnetic separation is the most dependable step in either route, which is why the shredded figure is barely below the dedicated one. The stream is steel, cast iron AND the ferrite magnets -- ferrite is ferrimagnetic and leaves with the ferrous fraction as an impurity in the steel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>F_recovered_fe_alloy</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>decision: unspecified material is not recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>F_recovered_fe_alloy</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- copper does not report to this stream. A structural zero, not a measurement: the separator sends it elsewhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>alalloy</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.225</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0.475</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.3375</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0.5875</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>fealloy</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>rest</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>decision: unspecified material is not recovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>F_shredded</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>component</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>F_loss_shredding</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0.3375</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>0.5875</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>shredding</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hammer_mill</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: 1 - what leaves in a stream, widened. This is the ASR and the fines.</t>
+          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation sqref="A2:A47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$D$2:$D$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="B2:B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$E$2:$E$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$F$2:$F$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$G$2:$G$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$H$2:$H$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$I$2:$I$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
-      <formula1>=_lists!$J$2:$J$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_folder/bev_electronics_metals/input_data/case.xlsx
+++ b/data_folder/bev_electronics_metals/input_data/case.xlsx
@@ -1282,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1297,7 +1297,6 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1348,20 +1347,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>is_residual</t>
+          <t>process</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>technology</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -1413,18 +1407,17 @@
           <t>0.95</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>disassembly</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>disassembly</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- a motor is a heavy, valuable, discrete part and a worker goes for it.</t>
         </is>
@@ -1466,26 +1459,29 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.105</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>disassembly</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever was not taken out is still in the car. Nothing is lost by not being disassembled.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -1527,18 +1523,17 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stays_in_car</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>stays_in_car</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>definitional</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>DEFINITIONAL: the car goes to the shredder, so what is in it goes too. Not a measurement and not uncertain.</t>
         </is>
@@ -1590,18 +1585,17 @@
           <t>0.4</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>disassembly</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>disassembly</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- pulling a harness out is slow manual work, so most of it stays in the car.</t>
         </is>
@@ -1643,26 +1637,29 @@
           <t>0.7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>disassembly</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>disassembly</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever was not taken out is still in the car. Nothing is lost by not being disassembled.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -1704,18 +1701,17 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stays_in_car</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>stays_in_car</t>
+          <t>definitional</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
-        <is>
-          <t>definitional</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>DEFINITIONAL: the car goes to the shredder, so what is in it goes too. Not a measurement and not uncertain.</t>
         </is>
@@ -1767,18 +1763,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>own_recycling</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
@@ -1820,26 +1815,29 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -1889,18 +1887,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>own_recycling</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
@@ -1942,26 +1939,29 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -2011,18 +2011,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>own_recycling</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
@@ -2064,26 +2063,29 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -2125,18 +2127,17 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>own_recycling</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
         <is>
           <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
@@ -2188,18 +2189,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>own_recycling</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
-        <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered on its own line, from a part that came out whole. This is the reason to disassemble at all.</t>
         </is>
@@ -2241,26 +2241,29 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>own_recycling</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>own_recycling</t>
+          <t>dedicated</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>dedicated</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -2310,18 +2313,17 @@
           <t>0.65</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for copper.</t>
         </is>
@@ -2363,26 +2365,29 @@
           <t>0.45</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -2432,18 +2437,17 @@
           <t>0.8</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for aluminium alloy.</t>
         </is>
@@ -2485,26 +2489,29 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -2554,18 +2561,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for steel alloy.</t>
         </is>
@@ -2607,26 +2613,29 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
@@ -2668,18 +2677,17 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
         <is>
           <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
@@ -2731,18 +2739,17 @@
           <t>0.65</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
-        <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
         <is>
           <t>PLACEHOLDER (Claude, not data) -- recovered from a shredded car. Crushing and tearing mixes everything, so less comes back -- most of all for copper.</t>
         </is>
@@ -2784,26 +2791,29 @@
           <t>0.45</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>general_recycling</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>general_recycling</t>
+          <t>shredder</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>shredder</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>COMPUTED, not typed: whatever did not reach the pile. The dust and the fragments too mixed to sort.</t>
+          <t>PLACEHOLDER (Claude, not data) -- NOT AN INDEPENDENT MEASUREMENT: it is 1 minus what left in the stream, given its own range. Replace it with a number measured on this side.</t>
         </is>
       </c>
     </row>
